--- a/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Myriam va au marché avec maman. Maman est l'accompagnant. Myriam aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds de Myriam restent près. Ils voient des cerises. Myriam reste avec l'accompagnant. L'adulte connu est là. Maman dit : tu restes avec moi. Myriam hoche la tête. Elle sent la main. La main est douce. Plus tard, elles vont à la bibliothèque. Les livres sentent le papier. Myriam se souvient. Elle reste avec l'accompagnant. Elle reste à côté de maman. Les pieds restent près. La main de maman est là. Maman dit : tu restes avec l'adulte connu. Myriam sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
+          <t>Myriam va au marché avec maman. Maman est l'accompagnant. Myriam aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds de Myriam restent près. Ils voient des cerises. Myriam reste avec l'accompagnant. L'adulte connu est là. Tu restes avec moi. Myriam hoche la tête. Elle sent la main. La main est douce. Plus tard, elles vont à la bibliothèque. Les livres sentent le papier. Myriam se souvient. Elle reste avec l'accompagnant. Elle reste à côté de maman. Les pieds restent près. La main de maman est là. Tu restes avec l'adulte connu. Myriam sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Myriam va au marché avec maman. Maman est l'accompagnant. Myriam aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds de Myriam restent près. Ils voient des cerises. Myriam reste avec l'accompagnant. L'adulte connu est là.
+maman|Tu restes avec moi.
+narrateur|Myriam hoche la tête. Elle sent la main. La main est douce. Plus tard, elles vont à la bibliothèque. Les livres sentent le papier. Myriam se souvient. Elle reste avec l'accompagnant. Elle reste à côté de maman. Les pieds restent près. La main de maman est là.
+maman|Tu restes avec l'adulte connu.
+narrateur|Myriam sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Myriam est au marché, puis à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Myriam reste avec maman. Au marché, puis à la bibliothèque. L'adulte connu est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Myriam et maman tiennent un livre. Elles restent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Myriam sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Myriam est au marché, puis à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Myriam reste avec maman. Au marché, puis à la bibliothèque. L'adulte connu est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Myriam et maman tiennent un livre. Elles restent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Myriam reste avec maman, deux lieux</t>
+          <t>Les cerises et le livre de papier</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les tentes claquent. Les cerises brillent. Puis les livres sentent le papier. Mila reste avec l'accompagnant, au marché et à la bibliothèque.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Myriam va au marché avec maman. Maman est l'accompagnant. Myriam aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds de Myriam restent près. Ils voient des cerises. Myriam reste avec l'accompagnant. L'adulte connu est là. Tu restes avec moi. Myriam hoche la tête. Elle sent la main. La main est douce. Plus tard, elles vont à la bibliothèque. Les livres sentent le papier. Myriam se souvient. Elle reste avec l'accompagnant. Elle reste à côté de maman. Les pieds restent près. La main de maman est là. Tu restes avec l'adulte connu. Myriam sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
+          <t>Les tentes du marché claquent un peu. Le vent les pousse, tout doux. Une tache rouge brille sur une caisse. C'est du jus de cerise. Le pavé est encore un peu mouillé. Ça sent le pain, tout près. Une balance fait tic. Puis encore tic. Un cabas sent le linge propre. Mila vit ici, avec maman. Maman, la tente claque ! Oui. C'est le vent. Tu vois les cerises ? Oui. Elles sont toutes rouges. En ce moment, elles marchent sous la tente. Maman tient la main de Mila. La main est douce, un peu chaude. Les pieds de Mila restent près. Maman est l'accompagnant. Mila aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Elles s'arrêtent devant les cerises. Une cerise a une petite queue. Elle brille comme un bijou. Elle est trop rouge ! Oui. On en prend un peu. Maman choisit les cerises. Mila reste à côté. Ses pieds restent près des pieds de maman. Tu restes bien près. Tu as fait du bon travail. Le sac en papier fait un petit bruit. Il sent le fruit sucré. Ça sent bon. Oui. Ça sent les cerises. Elles paient à la balance. La balance fait encore tic. On reste ensemble. Je reste avec l'accompagnant. Oui. Bravo, Mila. Plus tard, le pavé devient plus calme. Elles marchent vers la bibliothèque. La main de maman reste dans la main de Mila. Les pieds restent près. La porte de la bibliothèque est lourde. Elle fait un petit souffle. Le tapis cache les pas. Ça sent le papier, tout doux. Ça sent les livres ! Oui. Tu restes avec moi, ici aussi. Mila se souvient. Ici aussi, elle reste près. Elle reste avec l'accompagnant. Elle reste à côté de maman. Un livre a une couverture bleue. Une poule jaune est dessus. La poule ! On le prend ensemble ? Oui. Maman prend le livre. Mila reste tout près. Tu restes avec l'adulte connu. Oui, maman. Bravo. Elles s'assoient un moment. Le banc est lisse, un peu froid. Maman ouvre une page. Le papier est mat, tout calme. Tu es bien près de moi ? Oui. Je reste avec l'accompagnant. C'est du bon travail. Elles referment le livre. Le sac de cerises pèse un peu. Elles sortent ensemble. Le vent touche encore les tentes, au loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,98 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Myriam va au marché avec maman. Maman est l'accompagnant. Myriam aime rester avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds de Myriam restent près. Ils voient des cerises. Myriam reste avec l'accompagnant. L'adulte connu est là.
-maman|Tu restes avec moi.
-narrateur|Myriam hoche la tête. Elle sent la main. La main est douce. Plus tard, elles vont à la bibliothèque. Les livres sentent le papier. Myriam se souvient. Elle reste avec l'accompagnant. Elle reste à côté de maman. Les pieds restent près. La main de maman est là.
+          <t>narrateur|Les tentes du marché claquent un peu.
+narrateur|Le vent les pousse, tout doux.
+narrateur|Une tache rouge brille sur une caisse.
+narrateur|C'est du jus de cerise.
+narrateur|Le pavé est encore un peu mouillé.
+narrateur|Ça sent le pain, tout près.
+narrateur|Une balance fait tic.
+narrateur|Puis encore tic.
+narrateur|Un cabas sent le linge propre.
+narrateur|Mila vit ici, avec maman.
+enfant-f|Maman, la tente claque !
+maman|Oui.
+maman|C'est le vent.
+maman|Tu vois les cerises ?
+enfant-f|Oui.
+enfant-f|Elles sont toutes rouges.
+narrateur|En ce moment, elles marchent sous la tente.
+narrateur|Maman tient la main de Mila.
+narrateur|La main est douce, un peu chaude.
+narrateur|Les pieds de Mila restent près.
+narrateur|Maman est l'accompagnant.
+narrateur|Mila aime rester avec l'accompagnant.
+maman|Tu restes avec moi ?
+enfant-f|Oui, maman.
+maman|Bravo.
 maman|Tu restes avec l'adulte connu.
-narrateur|Myriam sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Elles s'arrêtent devant les cerises.
+narrateur|Une cerise a une petite queue.
+narrateur|Elle brille comme un bijou.
+enfant-f|Elle est trop rouge !
+maman|Oui.
+maman|On en prend un peu.
+narrateur|Maman choisit les cerises.
+narrateur|Mila reste à côté.
+narrateur|Ses pieds restent près des pieds de maman.
+maman|Tu restes bien près.
+maman|Tu as fait du bon travail.
+narrateur|Le sac en papier fait un petit bruit.
+narrateur|Il sent le fruit sucré.
+enfant-f|Ça sent bon.
+maman|Oui.
+maman|Ça sent les cerises.
+narrateur|Elles paient à la balance.
+narrateur|La balance fait encore tic.
+maman|On reste ensemble.
+enfant-f|Je reste avec l'accompagnant.
+maman|Oui.
+maman|Bravo, Mila.
+narrateur|Plus tard, le pavé devient plus calme.
+narrateur|Elles marchent vers la bibliothèque.
+narrateur|La main de maman reste dans la main de Mila.
+narrateur|Les pieds restent près.
+narrateur|La porte de la bibliothèque est lourde.
+narrateur|Elle fait un petit souffle.
+narrateur|Le tapis cache les pas.
+narrateur|Ça sent le papier, tout doux.
+enfant-f|Ça sent les livres !
+maman|Oui.
+maman|Tu restes avec moi, ici aussi.
+narrateur|Mila se souvient.
+narrateur|Ici aussi, elle reste près.
+narrateur|Elle reste avec l'accompagnant.
+narrateur|Elle reste à côté de maman.
+narrateur|Un livre a une couverture bleue.
+narrateur|Une poule jaune est dessus.
+enfant-f|La poule !
+maman|On le prend ensemble ?
+enfant-f|Oui.
+narrateur|Maman prend le livre.
+narrateur|Mila reste tout près.
+maman|Tu restes avec l'adulte connu.
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Elles s'assoient un moment.
+narrateur|Le banc est lisse, un peu froid.
+narrateur|Maman ouvre une page.
+narrateur|Le papier est mat, tout calme.
+maman|Tu es bien près de moi ?
+enfant-f|Oui.
+enfant-f|Je reste avec l'accompagnant.
+maman|C'est du bon travail.
+narrateur|Elles referment le livre.
+narrateur|Le sac de cerises pèse un peu.
+narrateur|Elles sortent ensemble.
+narrateur|Le vent touche encore les tentes, au loin.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>marche,livres</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1440,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Myriam est au marché, puis à la bibliothèque. Que fait-elle ?</t>
+          <t>Mila est au marché, puis à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1600,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Myriam est au marché, puis à la bibliothèque. Que fait-elle ?</t>
+          <t>narrateur|Mila est au marché, puis à la bibliothèque.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1629,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Myriam reste avec maman. Au marché, puis à la bibliothèque. L'adulte connu est là.</t>
+          <t>Mila reste avec maman. Au marché, puis à la bibliothèque. Maman est l'accompagnant. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Mila. Tu restes avec l'adulte connu. Le livre bleu reste dans le cabas. Les cerises sentent encore le sucre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1773,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Myriam reste avec maman. Au marché, puis à la bibliothèque. L'adulte connu est là.</t>
+          <t>narrateur|Mila reste avec maman.
+narrateur|Au marché, puis à la bibliothèque.
+narrateur|Maman est l'accompagnant.
+maman|Tu restes avec l'accompagnant ?
+enfant-f|Oui.
+enfant-f|Avec toi.
+maman|Bravo, Mila.
+maman|Tu restes avec l'adulte connu.
+narrateur|Le livre bleu reste dans le cabas.
+narrateur|Les cerises sentent encore le sucre.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1810,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Myriam et maman tiennent un livre. Elles restent ensemble.</t>
+          <t>Sur le chemin, le pavé sèche. Tu tiens encore ma main ? Oui, maman. Bravo. Elles rentrent à la maison. Le cabas pose un bruit doux. Tu as fini de marcher près de moi ? Oui. Tu as fait du bon travail. Une cerise roule un peu dans le sac. Le livre bleu attend sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1950,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Myriam et maman tiennent un livre. Elles restent ensemble.</t>
+          <t>narrateur|Sur le chemin, le pavé sèche.
+maman|Tu tiens encore ma main ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Elles rentrent à la maison.
+narrateur|Le cabas pose un bruit doux.
+maman|Tu as fini de marcher près de moi ?
+enfant-f|Oui.
+maman|Tu as fait du bon travail.
+narrateur|Une cerise roule un peu dans le sac.
+narrateur|Le livre bleu attend sur la table.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1988,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis restée avec maman. Avec l'accompagnant. Bravo. C'est du bon travail. Les tentes du marché se taisent. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2128,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je suis restée avec maman.
+maman|Avec l'accompagnant.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|Les tentes du marché se taisent.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2193,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les tentes du marché claquent un peu. Le vent les pousse, tout doux. Une tache rouge brille sur une caisse. C'est du jus de cerise. Le pavé est encore un peu mouillé. Ça sent le pain, tout près. Une balance fait tic. Puis encore tic. Un cabas sent le linge propre. Mila vit ici, avec maman. Maman, la tente claque ! Oui. C'est le vent. Tu vois les cerises ? Oui. Elles sont toutes rouges. En ce moment, elles marchent sous la tente. Maman tient la main de Mila. La main est douce, un peu chaude. Les pieds de Mila restent près. Maman est l'accompagnant. Mila aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Elles s'arrêtent devant les cerises. Une cerise a une petite queue. Elle brille comme un bijou. Elle est trop rouge ! Oui. On en prend un peu. Maman choisit les cerises. Mila reste à côté. Ses pieds restent près des pieds de maman. Tu restes bien près. Tu as fait du bon travail. Le sac en papier fait un petit bruit. Il sent le fruit sucré. Ça sent bon. Oui. Ça sent les cerises. Elles paient à la balance. La balance fait encore tic. On reste ensemble. Je reste avec l'accompagnant. Oui. Bravo, Mila. Plus tard, le pavé devient plus calme. Elles marchent vers la bibliothèque. La main de maman reste dans la main de Mila. Les pieds restent près. La porte de la bibliothèque est lourde. Elle fait un petit souffle. Le tapis cache les pas. Ça sent le papier, tout doux. Ça sent les livres ! Oui. Tu restes avec moi, ici aussi. Mila se souvient. Ici aussi, elle reste près. Elle reste avec l'accompagnant. Elle reste à côté de maman. Un livre a une couverture bleue. Une poule jaune est dessus. La poule ! On le prend ensemble ? Oui. Maman prend le livre. Mila reste tout près. Tu restes avec l'adulte connu. Oui, maman. Bravo. Elles s'assoient un moment. Le banc est lisse, un peu froid. Maman ouvre une page. Le papier est mat, tout calme. Tu es bien près de moi ? Oui. Je reste avec l'accompagnant. C'est du bon travail. Elles referment le livre. Le sac de cerises pèse un peu. Elles sortent ensemble. Le vent touche encore les tentes, au loin.</t>
+          <t>Les tentes du marché claquent un peu. Le vent les pousse, tout doux. Une tache rouge brille sur une caisse. C'est du jus de cerise. Le pavé est encore un peu mouillé. Ça sent le pain, tout près. Une balance fait tic. Puis encore tic. Un cabas sent le linge propre. Mila vit ici, avec maman. Maman, la tente claque ! Oui. C'est le vent. Tu vois les cerises ? Oui. Elles sont toutes rouges. En ce moment, elles marchent sous la tente. Maman tient la main de Mila. La main est douce, un peu chaude. Les pieds de Mila restent près. Maman est l'accompagnant. Mila aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Elles s'arrêtent devant les cerises. Une cerise a une petite queue. Elle brille comme un bijou. Elle est trop rouge ! Oui. On en prend un peu. Maman choisit les cerises. Mila reste à côté. Ses pieds restent près des pieds de maman. Tu restes bien près. Le sac en papier fait un petit bruit. Il sent le fruit sucré. Ça sent bon. Oui. Ça sent les cerises. Elles paient à la balance. La balance fait encore tic. On reste ensemble. Je reste avec l'accompagnant. Oui. Bravo, Mila. Plus tard, le pavé devient plus calme. Elles marchent vers la bibliothèque. La main de maman reste dans la main de Mila. Les pieds restent près. La porte de la bibliothèque est lourde. Elle fait un petit souffle. Le tapis cache les pas. Ça sent le papier, tout doux. Ça sent les livres ! Oui. Tu restes avec moi, ici aussi. Mila se souvient. Ici aussi, elle reste près. Elle reste avec l'accompagnant. Elle reste à côté de maman. Un livre a une couverture bleue. Une poule jaune est dessus. La poule ! On le prend ensemble ? Oui. Maman prend le livre. Mila reste tout près. Tu restes avec l'adulte connu. Oui, maman. Bravo. Elles s'assoient un moment. Le banc est lisse, un peu froid. Maman ouvre une page. Le papier est mat, tout calme. Tu es bien près de moi ? Oui. Je reste avec l'accompagnant. Elles referment le livre. Le sac de cerises pèse un peu. Elles sortent ensemble. Le vent touche encore les tentes, au loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Myriam va au marché avec maman. Maman est l'accompagnant. Myriam aime &lt;emphasis level="moderate"&gt;rester&lt;/emphasis&gt; avec l'accompagnant. Elle marche à côté de maman. Maman tient la main. Les pieds de Myriam restent près. Ils voient des cerises. Myriam reste avec l'accompagnant. L'adulte connu est là. Maman dit : tu restes avec moi. Myriam hoche la tête. Elle sent la main. La main est douce. Plus tard, elles vont à la bibliothèque. Les livres sentent le papier. Myriam se souvient. Elle reste avec l'accompagnant. Elle reste à côté de maman. Les pieds restent près. La main de maman est là. Maman dit : tu restes avec l'adulte connu. Myriam sourit. Même leçon, autre lieu. L'accompagnant de la famille est là.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les tentes du marché claquent un peu. Le vent les pousse, tout doux. Une tache rouge brille sur une caisse. C'est du jus de cerise. Le pavé est encore un peu mouillé. Ça sent le pain, tout près. Une balance fait tic. Puis encore tic. Un cabas sent le linge propre. Mila vit ici, avec maman. Maman, la tente claque ! Oui. C'est le vent. Tu vois les cerises ? Oui. Elles sont toutes rouges. En ce moment, elles marchent sous la tente. Maman tient la main de Mila. La main est douce, un peu chaude. Les pieds de Mila restent près. Maman est l'accompagnant. Mila aime rester avec l'accompagnant. Tu restes avec moi ? Oui, maman. Bravo. Tu restes avec l'adulte connu. Elles s'arrêtent devant les cerises. Une cerise a une petite queue. Elle brille comme un bijou. Elle est trop rouge ! Oui. On en prend un peu. Maman choisit les cerises. Mila reste à côté. Ses pieds restent près des pieds de maman. Tu restes bien près. Le sac en papier fait un petit bruit. Il sent le fruit sucré. Ça sent bon. Oui. Ça sent les cerises. Elles paient à la balance. La balance fait encore tic. On reste ensemble. Je reste avec l'accompagnant. Oui. Bravo, Mila. Plus tard, le pavé devient plus calme. Elles marchent vers la bibliothèque. La main de maman reste dans la main de Mila. Les pieds restent près. La porte de la bibliothèque est lourde. Elle fait un petit souffle. Le tapis cache les pas. Ça sent le papier, tout doux. Ça sent les livres ! Oui. Tu restes avec moi, ici aussi. Mila se souvient. Ici aussi, elle reste près. Elle reste avec l'accompagnant. Elle reste à côté de maman. Un livre a une couverture bleue. Une poule jaune est dessus. La poule ! On le prend ensemble ? Oui. Maman prend le livre. Mila reste tout près. Tu restes avec l'adulte connu. Oui, maman. Bravo. Elles s'assoient un moment. Le banc est lisse, un peu froid. Maman ouvre une page. Le papier est mat, tout calme. Tu es bien près de moi ? Oui. Je reste avec l'accompagnant. Elles referment le livre. Le sac de cerises pèse un peu. Elles sortent ensemble. Le vent touche encore les tentes, au loin.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1360,7 +1360,6 @@
 narrateur|Mila reste à côté.
 narrateur|Ses pieds restent près des pieds de maman.
 maman|Tu restes bien près.
-maman|Tu as fait du bon travail.
 narrateur|Le sac en papier fait un petit bruit.
 narrateur|Il sent le fruit sucré.
 enfant-f|Ça sent bon.
@@ -1404,7 +1403,6 @@
 maman|Tu es bien près de moi ?
 enfant-f|Oui.
 enfant-f|Je reste avec l'accompagnant.
-maman|C'est du bon travail.
 narrateur|Elles referment le livre.
 narrateur|Le sac de cerises pèse un peu.
 narrateur|Elles sortent ensemble.
@@ -1445,7 +1443,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Myriam est au marché, puis à la bibliothèque. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est au marché, puis à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1604,7 +1602,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1634,7 +1631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Myriam reste avec maman. Au marché, puis à la bibliothèque. L'adulte connu est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila reste avec maman. Au marché, puis à la bibliothèque. Maman est l'accompagnant. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Mila. Tu restes avec l'adulte connu. Le livre bleu reste dans le cabas. Les cerises sentent encore le sucre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1785,7 +1782,6 @@
 narrateur|Les cerises sentent encore le sucre.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1810,12 +1806,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, le pavé sèche. Tu tiens encore ma main ? Oui, maman. Bravo. Elles rentrent à la maison. Le cabas pose un bruit doux. Tu as fini de marcher près de moi ? Oui. Tu as fait du bon travail. Une cerise roule un peu dans le sac. Le livre bleu attend sur la table.</t>
+          <t>Sur le chemin, le pavé sèche. Tu tiens encore ma main ? Oui, maman. Bravo. Elles rentrent à la maison. Le cabas pose un bruit doux. Tu as fini de marcher près de moi ? Oui. Une cerise roule un peu dans le sac. Le livre bleu attend sur la table.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Myriam et maman tiennent un livre. Elles restent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le chemin, le pavé sèche. Tu tiens encore ma main ? Oui, maman. Bravo. Elles rentrent à la maison. Le cabas pose un bruit doux. Tu as fini de marcher près de moi ? Oui. Une cerise roule un peu dans le sac. Le livre bleu attend sur la table.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1958,12 +1954,10 @@
 narrateur|Le cabas pose un bruit doux.
 maman|Tu as fini de marcher près de moi ?
 enfant-f|Oui.
-maman|Tu as fait du bon travail.
 narrateur|Une cerise roule un peu dans le sac.
 narrateur|Le livre bleu attend sur la table.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1988,12 +1982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis restée avec maman. Avec l'accompagnant. Bravo. C'est du bon travail. Les tentes du marché se taisent. L'histoire est finie.</t>
+          <t>Je suis restée avec maman. Avec l'accompagnant. Bravo. Les tentes du marché se taisent.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis restée avec maman. Avec l'accompagnant. Bravo. Les tentes du marché se taisent.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2131,12 +2125,9 @@
           <t>enfant-f|Je suis restée avec maman.
 maman|Avec l'accompagnant.
 maman|Bravo.
-maman|C'est du bon travail.
-narrateur|Les tentes du marché se taisent.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les tentes du marché se taisent.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2155,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2200,6 +2191,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marché puis bibliothèque</t>
+          <t>marché du village puis bibliothèque</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Myriam, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
